--- a/stories/arbres/TREE-SEC-019.xlsx
+++ b/stories/arbres/TREE-SEC-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est avec maman, à l'école. Tom a envie de jouer. maman est là, tout près. On va apprendre : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom écoute maman. Tom entend les mots : trottoir, s'arrêter, pieds au bord.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1870,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2047,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2197,6 +2240,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -2365,6 +2413,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon rouge. La couverture est douce. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2553,6 +2606,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2721,6 +2779,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2883,6 +2946,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3049,6 +3117,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3211,6 +3284,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3377,6 +3455,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3539,6 +3622,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3705,6 +3793,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau bleu. On entend un oiseau. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3893,6 +3986,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4061,6 +4159,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4223,6 +4326,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4389,6 +4497,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4551,6 +4664,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4717,6 +4835,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4879,6 +5002,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5045,6 +5173,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5233,6 +5366,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5401,6 +5539,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5563,6 +5706,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5729,6 +5877,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5891,6 +6044,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6057,6 +6215,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6219,6 +6382,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6243,7 +6411,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6385,6 +6553,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6569,6 +6743,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
     </row>
@@ -6741,6 +6920,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6929,6 +7113,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -7097,6 +7286,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon rouge. Le vent est doux. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7285,6 +7479,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7453,6 +7652,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7615,6 +7819,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7781,6 +7990,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7943,6 +8157,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8109,6 +8328,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8271,6 +8495,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8437,6 +8666,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau bleu. Le sol est un peu froid. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8625,6 +8859,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8793,6 +9032,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8955,6 +9199,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9121,6 +9370,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9283,6 +9537,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9449,6 +9708,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9611,6 +9875,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9777,6 +10046,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9965,6 +10239,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10133,6 +10412,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10295,6 +10579,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10461,6 +10750,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10623,6 +10917,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10789,6 +11088,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10951,6 +11255,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10975,7 +11284,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11117,6 +11426,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Tom se souvient : trottoir, s'arrêter, pieds au bord. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11301,6 +11616,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
     </row>
@@ -11473,6 +11793,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11661,6 +11986,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -11829,6 +12159,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le ballon rouge. L'eau coule, tout petit bruit. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12017,6 +12352,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12185,6 +12525,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12347,6 +12692,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12513,6 +12863,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12675,6 +13030,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12841,6 +13201,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13003,6 +13368,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13169,6 +13539,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le seau bleu. Un vélo passe au loin. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13357,6 +13732,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13525,6 +13905,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13687,6 +14072,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13853,6 +14243,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14015,6 +14410,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14181,6 +14581,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14343,6 +14748,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14509,6 +14919,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14697,6 +15112,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14865,6 +15285,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15027,6 +15452,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15193,6 +15623,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15355,6 +15790,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15521,6 +15961,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15683,6 +16128,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15701,7 +16151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15795,6 +16245,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-019.xlsx
+++ b/stories/arbres/TREE-SEC-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Tom est avec maman, à l'école. Tom a envie de jouer. maman est là, tout près. On va apprendre : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom écoute maman. Tom entend les mots : trottoir, s'arrêter, pieds au bord.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1877,6 +1885,7 @@
           <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2052,6 +2061,7 @@
           <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2247,6 +2257,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2418,6 +2429,7 @@
           <t>narrateur|Tom a choisi le ballon rouge. La couverture est douce. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2613,6 +2625,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2784,6 +2797,7 @@
           <t>narrateur|Tom rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2951,6 +2965,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3122,6 +3137,7 @@
           <t>narrateur|Tom rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3289,6 +3305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3460,6 +3477,7 @@
           <t>narrateur|Tom rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3627,6 +3645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3798,6 +3817,7 @@
           <t>narrateur|Tom a choisi le seau bleu. On entend un oiseau. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3993,6 +4013,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4164,6 +4185,7 @@
           <t>narrateur|Tom rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4331,6 +4353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4502,6 +4525,7 @@
           <t>narrateur|Tom rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4669,6 +4693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4840,6 +4865,7 @@
           <t>narrateur|Tom rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5007,6 +5033,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5178,6 +5205,7 @@
           <t>narrateur|Tom a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5373,6 +5401,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5544,6 +5573,7 @@
           <t>narrateur|Tom rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5711,6 +5741,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5882,6 +5913,7 @@
           <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6049,6 +6081,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6220,6 +6253,7 @@
           <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6387,6 +6421,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6559,6 +6594,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6750,6 +6786,7 @@
           <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6925,6 +6962,7 @@
           <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7120,6 +7158,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7291,6 +7330,7 @@
           <t>narrateur|Tom a choisi le ballon rouge. Le vent est doux. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7486,6 +7526,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7657,6 +7698,7 @@
           <t>narrateur|Tom rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7824,6 +7866,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7995,6 +8038,7 @@
           <t>narrateur|Tom rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8162,6 +8206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8333,6 +8378,7 @@
           <t>narrateur|Tom rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8500,6 +8546,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8671,6 +8718,7 @@
           <t>narrateur|Tom a choisi le seau bleu. Le sol est un peu froid. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8866,6 +8914,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9037,6 +9086,7 @@
           <t>narrateur|Tom rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9204,6 +9254,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9375,6 +9426,7 @@
           <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9542,6 +9594,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9713,6 +9766,7 @@
           <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9880,6 +9934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10051,6 +10106,7 @@
           <t>narrateur|Tom a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10246,6 +10302,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10417,6 +10474,7 @@
           <t>narrateur|Tom rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10584,6 +10642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10755,6 +10814,7 @@
           <t>narrateur|Tom rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10922,6 +10982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11093,6 +11154,7 @@
           <t>narrateur|Tom rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11260,6 +11322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11432,6 +11495,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11623,6 +11687,7 @@
           <t>narrateur|Que fait-on ? S'arrêter au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11798,6 +11863,7 @@
           <t>narrateur|Oui. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom respire. Tom retient : trottoir, s'arrêter, pieds au bord. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11993,6 +12059,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12164,6 +12231,7 @@
           <t>narrateur|Tom a choisi le ballon rouge. L'eau coule, tout petit bruit. Le ballon rouge reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12359,6 +12427,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12530,6 +12599,7 @@
           <t>narrateur|Tom rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon rouge et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12697,6 +12767,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12868,6 +12939,7 @@
           <t>narrateur|Tom rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon rouge et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13035,6 +13107,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13206,6 +13279,7 @@
           <t>narrateur|Tom rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon rouge et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13373,6 +13447,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13544,6 +13619,7 @@
           <t>narrateur|Tom a choisi le seau bleu. Un vélo passe au loin. Le seau bleu reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13739,6 +13815,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13910,6 +13987,7 @@
           <t>narrateur|Tom rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau bleu et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14077,6 +14155,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14248,6 +14327,7 @@
           <t>narrateur|Tom rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau bleu et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14415,6 +14495,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14586,6 +14667,7 @@
           <t>narrateur|Tom rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau bleu et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14753,6 +14835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14924,6 +15007,7 @@
           <t>narrateur|Tom a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom répète tout bas : trottoir, s'arrêter, pieds au bord. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15119,6 +15203,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15290,6 +15375,7 @@
           <t>narrateur|Tom rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15457,6 +15543,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15628,6 +15715,7 @@
           <t>narrateur|Tom rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15795,6 +15883,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15966,6 +16055,7 @@
           <t>narrateur|Tom rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Tom a appris : S'arrêter au bord du trottoir. Voici le geste : s'arrêter ; pieds sur le trottoir ; attendre l'adulte. Tom a entendu : trottoir, s'arrêter, pieds au bord. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16133,6 +16223,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16151,7 +16242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16252,6 +16343,20 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16453,6 +16558,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
